--- a/pensum/ma09/MA09_Pavirkning_Regneark_Pavirkning.xlsx
+++ b/pensum/ma09/MA09_Pavirkning_Regneark_Pavirkning.xlsx
@@ -1034,7 +1034,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1193,6 +1193,10 @@
     </xf>
     <xf numFmtId="169" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1828,8 +1832,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="17" t="s">
+    <row ht="27" customHeight="true" r="30" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="40" r="A30" t="s">
         <v>63</v>
       </c>
       <c r="B30" s="19" t="s">
@@ -2406,7 +2410,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="39.75" customHeight="true" r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="20"/>
       <c r="B4" s="20" t="s">
         <v>125</v>
@@ -3484,44 +3488,44 @@
         <v>232</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="42" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="17" t="s">
         <v>233</v>
       </c>
-      <c r="B42" s="17" t="s">
+      <c s="40" r="B42" t="s">
         <v>234</v>
       </c>
       <c r="C42" s="17" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="43" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="17" t="s">
         <v>236</v>
       </c>
-      <c r="B43" s="17" t="s">
+      <c s="40" r="B43" t="s">
         <v>237</v>
       </c>
       <c r="C43" s="17" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="44" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="B44" s="17" t="s">
+      <c s="40" r="B44" t="s">
         <v>239</v>
       </c>
       <c r="C44" s="17" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row ht="52.5" customHeight="true" r="45" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="17" t="s">
         <v>241</v>
       </c>
-      <c r="B45" s="17" t="s">
+      <c s="40" r="B45" t="s">
         <v>242</v>
       </c>
       <c r="C45" s="17" t="s">
